--- a/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260805.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260805.xlsx
@@ -1041,17 +1041,17 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2105</t>
+          <t>2855</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>正新</t>
+          <t>統一證</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>119,300,000</t>
+          <t>79,690,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -1063,17 +1063,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2855</t>
+          <t>2105</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>統一證</t>
+          <t>正新</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>79,690,000</t>
+          <t>119,300,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>4763</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>材料*-KY</t>
+          <t>東陽</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>41,500,000</t>
+          <t>27,850,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>4763</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>東陽</t>
+          <t>材料*-KY</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>27,850,000</t>
+          <t>41,500,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
